--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="316">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,10 @@
   </si>
   <si>
     <t>The maximum total quantity of a therapeutic substance that may be administered to a subject per administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -5469,10 +5473,10 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -5480,10 +5484,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5509,14 +5513,14 @@
         <v>305</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5565,22 +5569,22 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="376">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -619,13 +619,208 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
+    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>.routeCode</t>
+  </si>
+  <si>
+    <t>RXR-1</t>
+  </si>
+  <si>
+    <t>Dosage.route.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.id</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.extension</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
   </si>
   <si>
-    <t>.routeCode</t>
-  </si>
-  <si>
-    <t>RXR-1</t>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>Dosage.route.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Dosage.route.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -677,16 +872,6 @@
     <t>Dosage.doseAndRate.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Dosage.doseAndRate.type</t>
   </si>
   <si>
@@ -803,10 +988,6 @@
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x].comparator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
   </si>
   <si>
     <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
@@ -1320,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL39"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.88671875" customWidth="true" bestFit="true"/>
@@ -1359,7 +1540,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="109.8359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3481,11 +3662,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3518,18 +3701,18 @@
         <v>79</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3543,29 +3726,25 @@
         <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3589,13 +3768,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3613,7 +3792,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>196</v>
+        <v>86</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3625,52 +3804,54 @@
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3707,19 +3888,19 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3731,21 +3912,21 @@
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3756,7 +3937,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3765,19 +3946,23 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -3825,25 +4010,25 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -3855,14 +4040,14 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3874,17 +4059,15 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -3921,31 +4104,31 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>87</v>
@@ -3956,21 +4139,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3979,21 +4162,21 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4017,57 +4200,57 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>221</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4090,19 +4273,19 @@
         <v>126</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4112,7 +4295,7 @@
         <v>20</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>20</v>
@@ -4139,17 +4322,19 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4164,22 +4349,20 @@
         <v>79</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4191,7 +4374,7 @@
         <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
@@ -4200,20 +4383,18 @@
         <v>126</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M27" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4261,7 +4442,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4276,22 +4457,20 @@
         <v>79</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>228</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4303,7 +4482,7 @@
         <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
@@ -4312,19 +4491,17 @@
         <v>126</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4373,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4388,10 +4565,10 @@
         <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4399,7 +4576,7 @@
         <v>237</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4419,19 +4596,21 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>85</v>
+        <v>239</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -4479,7 +4658,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>86</v>
+        <v>241</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4491,32 +4670,32 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4525,21 +4704,23 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -4575,45 +4756,45 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4636,19 +4817,19 @@
         <v>126</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4697,7 +4878,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4712,18 +4893,18 @@
         <v>79</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" hidden="true">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4734,36 +4915,36 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>126</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>20</v>
       </c>
@@ -4783,13 +4964,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -4822,18 +5003,18 @@
         <v>79</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4847,7 +5028,7 @@
         <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
@@ -4856,18 +5037,16 @@
         <v>126</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>83</v>
+        <v>270</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -4891,11 +5070,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -4919,7 +5100,7 @@
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -4928,18 +5109,18 @@
         <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4959,21 +5140,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5021,7 +5200,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>277</v>
+        <v>86</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5030,35 +5209,35 @@
         <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>278</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>87</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5067,23 +5246,21 @@
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>200</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>201</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5119,45 +5296,45 @@
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>95</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5180,19 +5357,17 @@
         <v>126</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5217,13 +5392,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5241,7 +5416,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5256,18 +5431,18 @@
         <v>79</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5290,19 +5465,19 @@
         <v>126</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5339,19 +5514,17 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5366,20 +5539,22 @@
         <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="38" hidden="true">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
       </c>
@@ -5391,7 +5566,7 @@
         <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -5400,19 +5575,19 @@
         <v>126</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -5461,7 +5636,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5473,23 +5648,25 @@
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>311</v>
+        <v>267</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
       </c>
@@ -5501,7 +5678,7 @@
         <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5510,17 +5687,19 @@
         <v>126</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5569,29 +5748,1225 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AG39" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AL39" t="s" s="2">
+      <c r="B43" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL39">
+  <autoFilter ref="A1:AL50">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5601,7 +6976,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI38">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-frequency-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
